--- a/data/trans_orig/IP19C04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19C04-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>635</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12736</t>
+          <t>12427</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41144</t>
+          <t>41002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46259</t>
+          <t>46291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33447</t>
+          <t>33624</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40792</t>
+          <t>40768</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77080</t>
+          <t>77389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86025</t>
+          <t>85946</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8407</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21144</t>
+          <t>20789</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23566</t>
+          <t>23059</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22381</t>
+          <t>22323</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38919</t>
+          <t>39719</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>207178</t>
+          <t>207533</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>219915</t>
+          <t>219509</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>222157</t>
+          <t>222664</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234898</t>
+          <t>234828</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>435126</t>
+          <t>434326</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>451664</t>
+          <t>451722</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8549</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8714</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14354</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67134</t>
+          <t>67682</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74161</t>
+          <t>73927</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64403</t>
+          <t>64416</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71511</t>
+          <t>71510</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134446</t>
+          <t>134722</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144089</t>
+          <t>144233</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14119</t>
+          <t>13855</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28552</t>
+          <t>28870</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19093</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>34049</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36529</t>
+          <t>35600</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58819</t>
+          <t>56580</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>322378</t>
+          <t>322060</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>336811</t>
+          <t>337075</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>326658</t>
+          <t>327682</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>342638</t>
+          <t>343266</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>653842</t>
+          <t>656081</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>676132</t>
+          <t>677061</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10700</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>14133</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37264</t>
+          <t>36592</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44767</t>
+          <t>44544</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37621</t>
+          <t>37516</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42366</t>
+          <t>42346</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76767</t>
+          <t>76795</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85723</t>
+          <t>86307</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21197</t>
+          <t>21371</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10385</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23857</t>
+          <t>23639</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22409</t>
+          <t>22575</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41050</t>
+          <t>40503</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>199281</t>
+          <t>199107</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211414</t>
+          <t>211595</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>217056</t>
+          <t>217274</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>230528</t>
+          <t>230507</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>420341</t>
+          <t>420888</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>438982</t>
+          <t>438816</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8567</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80323</t>
+          <t>80813</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75315</t>
+          <t>75853</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81431</t>
+          <t>81440</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>159106</t>
+          <t>159151</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>166135</t>
+          <t>166195</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31414</t>
+          <t>31640</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15142</t>
+          <t>14294</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29179</t>
+          <t>29573</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33459</t>
+          <t>33571</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55034</t>
+          <t>54266</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>322577</t>
+          <t>322351</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>338130</t>
+          <t>338332</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>336823</t>
+          <t>336429</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>350860</t>
+          <t>351708</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>664959</t>
+          <t>665727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>686534</t>
+          <t>686422</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>569</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>720</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6345</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17827</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22163</t>
+          <t>22152</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24544</t>
+          <t>24222</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44518</t>
+          <t>44848</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50135</t>
+          <t>50143</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21109</t>
+          <t>21535</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18195</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18351</t>
+          <t>17775</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33821</t>
+          <t>33998</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>231631</t>
+          <t>231205</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>243426</t>
+          <t>242965</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>234610</t>
+          <t>234888</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>245769</t>
+          <t>246006</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>471724</t>
+          <t>471547</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>487194</t>
+          <t>487770</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>691</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8292</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>736</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10875</t>
+          <t>10710</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79448</t>
+          <t>80259</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86966</t>
+          <t>87049</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81196</t>
+          <t>81428</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86964</t>
+          <t>86962</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>164562</t>
+          <t>164727</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>173262</t>
+          <t>172911</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26731</t>
+          <t>27656</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>21615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>25839</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44038</t>
+          <t>43764</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>336470</t>
+          <t>335545</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>350131</t>
+          <t>349844</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346901</t>
+          <t>347029</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>359626</t>
+          <t>359390</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>687807</t>
+          <t>688081</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>706474</t>
+          <t>706006</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26373</t>
+          <t>26508</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20880</t>
+          <t>20499</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49238</t>
+          <t>48977</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54827</t>
+          <t>54835</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7968</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21349</t>
+          <t>21904</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17897</t>
+          <t>18342</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16134</t>
+          <t>16309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33867</t>
+          <t>33769</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>240478</t>
+          <t>239923</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>253859</t>
+          <t>253893</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>305118</t>
+          <t>304673</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>317131</t>
+          <t>316972</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>550975</t>
+          <t>551073</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>568708</t>
+          <t>568533</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10046</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>14352</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90882</t>
+          <t>91598</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98101</t>
+          <t>98146</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125899</t>
+          <t>127282</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134863</t>
+          <t>135056</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>222460</t>
+          <t>221669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>231687</t>
+          <t>232184</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>12298</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>27037</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>9669</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23604</t>
+          <t>23862</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25192</t>
+          <t>24239</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45601</t>
+          <t>45443</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>364133</t>
+          <t>364596</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>380314</t>
+          <t>379335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>460840</t>
+          <t>460582</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>474552</t>
+          <t>474775</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>830475</t>
+          <t>830633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>850884</t>
+          <t>851837</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19C04-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4835</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2249</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9288</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,27%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,65%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2553</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5924</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5852</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,44%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4835</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2123</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9267</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,27%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>12536</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38056</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>33603</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>40642</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,73%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78,35%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,76%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>44373</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41002</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>46291</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41074</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>46278</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,56%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,38%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>38056</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>33624</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>40768</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,73%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77389</t>
+          <t>77280</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85946</t>
+          <t>85673</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16461</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10823</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23528</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>13934</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8813</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20789</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9082</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21791</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,1%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,11%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16461</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10895</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>23059</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22323</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39719</t>
+          <t>40344</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>229262</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>222195</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>234900</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,3%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>323</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>214388</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>207533</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>219509</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>206531</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>219240</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,9%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,89%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>229262</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>222664</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>234828</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,3%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>434326</t>
+          <t>433701</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>451722</t>
+          <t>451643</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>343</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1414,67 +1414,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>4323</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1469</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8136</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,13%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>4032</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1756</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8001</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8306</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,33%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4323</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1607</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8701</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>14100</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -1527,67 +1527,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>68794</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>64981</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>71648</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,09%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,87%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>71651</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67682</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>73927</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>67377</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>74275</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,67%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,43%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,68%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>68794</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>64416</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>71510</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,09%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134722</t>
+          <t>134700</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144233</t>
+          <t>144286</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -1640,52 +1640,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>75683</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25619</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18948</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>34357</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>20519</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13855</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14407</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>28733</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,85%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>25619</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>18465</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>34049</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35600</t>
+          <t>36483</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56580</t>
+          <t>57423</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>336112</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>327374</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>342783</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,92%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,5%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,76%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>330411</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>322060</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>337075</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>322197</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>336523</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,15%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,77%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,05%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>336112</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>327682</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>343266</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,92%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>656081</t>
+          <t>655238</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>677061</t>
+          <t>676178</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5541</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,9%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6504</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3420</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11372</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3328</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11507</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>13,56%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5447</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14133</t>
+          <t>13805</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>40973</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>37422</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>42360</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,1%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>41460</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>36592</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>44544</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>36457</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>44636</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>86,44%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>76,29%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,87%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>40973</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>37516</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>42346</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,37%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76795</t>
+          <t>77123</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86307</t>
+          <t>86407</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16214</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10545</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24606</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>14200</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8883</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21371</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9016</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21575</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,44%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16214</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10406</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>23639</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,73%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40503</t>
+          <t>40791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>224699</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>216307</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>230368</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,62%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>295</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>206278</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>199107</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>211595</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>198903</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>211462</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,56%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,31%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,97%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>224699</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>217274</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>230507</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,27%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>420888</t>
+          <t>420600</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>438816</t>
+          <t>439040</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>315</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>220478</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>220478</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>220478</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2774</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6212</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1516</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4735</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,77%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2774</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6272</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>79351</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>75913</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>81446</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,44%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>84032</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>80813</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>80218</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>85548</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,23%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,47%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>93,77%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>79351</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>75853</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>81440</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,62%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>92,36%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>232</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>159151</t>
+          <t>159512</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>166195</t>
+          <t>165775</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20978</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14563</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>28916</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>22220</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15659</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>31640</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15946</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>31191</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,28%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,94%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>20978</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>14294</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>29573</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33571</t>
+          <t>33116</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54266</t>
+          <t>55403</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>345024</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>337086</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>351439</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,1%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>472</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>331771</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>322351</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>338332</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>322800</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>338045</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,72%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,06%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>345024</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>336429</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>351708</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,27%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>665727</t>
+          <t>664590</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>686422</t>
+          <t>686877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>353991</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3655</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1900</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>569</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5164</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4840</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,36%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>22,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>727</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3919</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>723</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>27414</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24486</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>20821</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17557</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22152</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17881</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>22157</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,64%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>77,27%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,49%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>27414</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>24222</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44848</t>
+          <t>44820</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50143</t>
+          <t>50140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22721</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22721</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22721</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11373</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6692</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18394</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>14190</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9775</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21535</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>8606</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>20540</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,61%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,52%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11373</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6799</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>17917</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17775</t>
+          <t>18266</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33998</t>
+          <t>34618</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>241432</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>234411</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>246113</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,5%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,72%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,35%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>238550</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>231205</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>242965</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>232200</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>244134</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,39%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>241432</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>234888</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>246006</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,5%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>471547</t>
+          <t>470927</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>487770</t>
+          <t>487279</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>252805</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>252805</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>252805</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>370</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>252805</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>252805</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>252805</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6347</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,24%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3091</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7481</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7196</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,52%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>736</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6270</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10710</t>
+          <t>10725</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -4733,67 +4733,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>85353</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>81351</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>86954</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,76%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>84649</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>80259</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>87049</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>80544</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>86841</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,48%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,47%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>85353</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>81428</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>86962</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,33%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>164727</t>
+          <t>164712</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>172911</t>
+          <t>173240</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>87740</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>87740</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>87740</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14445</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8866</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22080</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,99%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>19181</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13357</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>27656</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>13055</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>27246</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,28%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>14445</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9254</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>21615</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25839</t>
+          <t>24962</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43764</t>
+          <t>44272</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>354199</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>346564</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>359778</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,01%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>500</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>344020</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>335545</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>349844</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>335955</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>350146</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,72%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,32%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>354199</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>347029</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>359390</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>688081</t>
+          <t>687573</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>706006</t>
+          <t>706883</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>368644</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>368644</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>368644</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>528</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>363201</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>363201</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>363201</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>368644</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>368644</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>368644</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1145</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5383</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>22,16%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3222</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3714</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1220</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4985</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>257</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -5645,74 +5645,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23145</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18907</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,28%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77,84%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>29017</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>26508</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>97,6%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,16%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>25970</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>22929</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>26643</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>97,47%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>86,06%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24264</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>20499</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>25484</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,21%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>80,44%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>65</t>
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>53281</t>
+          <t>49114</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48977</t>
+          <t>45034</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54835</t>
+          <t>50676</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9862</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5541</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17287</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13268</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7934</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21904</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6043</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18342</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>24093</t>
+          <t>22054</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16309</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33769</t>
+          <t>31110</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>299683</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>292258</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>304004</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,81%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,21%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>248559</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>239923</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>253893</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>94,93%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>312190</t>
+          <t>253861</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>304673</t>
+          <t>246767</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>316972</t>
+          <t>258648</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>560749</t>
+          <t>553543</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>551073</t>
+          <t>544487</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>568533</t>
+          <t>560071</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>367</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3426</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7929</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4399</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1930</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8478</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14352</t>
+          <t>14189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>123834</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>119331</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>126337</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,77%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>95677</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>91598</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>98146</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,53%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>132382</t>
+          <t>99224</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127282</t>
+          <t>94599</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135056</t>
+          <t>101710</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,17 +6406,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>228059</t>
+          <t>223057</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>221669</t>
+          <t>216653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>232184</t>
+          <t>226663</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14433</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8914</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22960</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>18379</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12298</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>27037</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>17224</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23862</t>
+          <t>25018</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>33988</t>
+          <t>31657</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24239</t>
+          <t>22739</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45443</t>
+          <t>42952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>446662</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>438135</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>452181</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>528</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>373254</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>364596</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>379335</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>95,31%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,86%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>468835</t>
+          <t>379054</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>460582</t>
+          <t>371260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>474775</t>
+          <t>384751</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>842088</t>
+          <t>825715</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>830633</t>
+          <t>814420</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>851837</t>
+          <t>834633</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
